--- a/Data/Stage/Stage.xlsx
+++ b/Data/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57AFAC3-15CC-457C-887A-7E9EF3F9FFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61188847-26D7-4BE4-9958-539F334D9A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="3405" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -347,10 +347,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:21">
       <c r="A1">
         <v>1</v>
       </c>
@@ -405,8 +405,17 @@
       <c r="R1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="S1">
+        <v>1</v>
+      </c>
+      <c r="T1">
+        <v>1</v>
+      </c>
+      <c r="U1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>1</v>
       </c>
@@ -459,10 +468,19 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>1</v>
       </c>
@@ -515,10 +533,19 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>1</v>
       </c>
@@ -571,10 +598,19 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5">
         <v>1</v>
       </c>
@@ -600,16 +636,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -627,10 +663,19 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>1</v>
       </c>
@@ -656,16 +701,16 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -683,10 +728,19 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>1</v>
       </c>
@@ -712,16 +766,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -741,8 +795,17 @@
       <c r="R7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>1</v>
       </c>
@@ -768,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -797,8 +860,17 @@
       <c r="R8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>1</v>
       </c>
@@ -824,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -853,8 +925,17 @@
       <c r="R9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>1</v>
       </c>
@@ -880,16 +961,16 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -909,8 +990,17 @@
       <c r="R10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>1</v>
       </c>
@@ -924,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -936,16 +1026,16 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -965,8 +1055,17 @@
       <c r="R11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>1</v>
       </c>
@@ -980,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -992,16 +1091,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -1013,16 +1112,25 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1036,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1048,16 +1156,16 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -1069,16 +1177,25 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1104,16 +1221,16 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -1125,16 +1242,25 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15">
         <v>1</v>
       </c>
@@ -1160,16 +1286,16 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1181,16 +1307,25 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1237,16 +1372,25 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1293,16 +1437,25 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1349,516 +1502,86 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21">
-        <v>1</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25">
-        <v>1</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26">
-        <v>1</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27">
-        <v>1</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-      <c r="P27">
-        <v>1</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-      <c r="R27">
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
         <v>1</v>
       </c>
     </row>
